--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_379_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_379_R38.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8977</v>
+        <v>7.2881</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6172</v>
+        <v>4.9728</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2804</v>
+        <v>2.3153</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6904</v>
+        <v>7.1882</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2687</v>
+        <v>3.3337</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4217</v>
+        <v>3.8545</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0766</v>
+        <v>7.2706</v>
       </c>
       <c r="K2" t="n">
-        <v>3.23</v>
+        <v>2.9913</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8465</v>
+        <v>4.2793</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3861</v>
+        <v>-0.0824</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0387</v>
+        <v>0.3424</v>
       </c>
       <c r="O2" t="n">
         <v>-0.4248</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3876</v>
+        <v>0.7389</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4169</v>
+        <v>0.1968</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9707</v>
+        <v>0.5421</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2836</v>
+        <v>2.1444</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2836</v>
+        <v>2.1444</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9419</v>
+        <v>6.3622</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9545</v>
+        <v>4.6867</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9875</v>
+        <v>1.6755</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1882</v>
+        <v>3.6904</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3337</v>
+        <v>3.2687</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8545</v>
+        <v>0.4217</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2706</v>
+        <v>4.0766</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9913</v>
+        <v>3.23</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2793</v>
+        <v>0.8465</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0824</v>
+        <v>-0.3861</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3424</v>
+        <v>0.0387</v>
       </c>
       <c r="O3" t="n">
         <v>-0.4248</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7834</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3927</v>
+        <v>2.8522</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8215</v>
+        <v>1.4864</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2142</v>
+        <v>1.3658</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1444</v>
+        <v>0.2836</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>0.2836</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2772</v>
+        <v>3.2217</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5511</v>
+        <v>2.2503</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7262</v>
+        <v>0.9714</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6058</v>
+        <v>0.4944</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8368</v>
+        <v>-0.4525</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4426</v>
+        <v>0.9469</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6634</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.729</v>
+        <v>-0.1443</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3923</v>
+        <v>1.0037</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0576</v>
+        <v>-0.365</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1078</v>
+        <v>-0.3082</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0502</v>
+        <v>-0.0568</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3673</v>
+        <v>0.2634</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9752</v>
+        <v>0.3187</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.608</v>
+        <v>-0.0553</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7784</v>
+        <v>3.011</v>
       </c>
       <c r="E5" t="n">
-        <v>3.327</v>
+        <v>1.4878</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5485</v>
+        <v>1.5233</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2826</v>
+        <v>2.1587</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1763</v>
+        <v>-0.1367</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4589</v>
+        <v>2.2953</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1588</v>
+        <v>1.9983</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9075</v>
+        <v>0.1715</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2514</v>
+        <v>1.8268</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8762</v>
+        <v>0.1603</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0838</v>
+        <v>-0.3082</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2075</v>
+        <v>0.4685</v>
       </c>
       <c r="P5" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5764</v>
+        <v>0.2467</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4402</v>
+        <v>0.5074</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1362</v>
+        <v>-0.2607</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7334</v>
+        <v>2.9636</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8964</v>
+        <v>3.4449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.837</v>
+        <v>-0.4813</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4944</v>
+        <v>1.2826</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4525</v>
+        <v>-0.1763</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9469</v>
+        <v>1.4589</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8594000000000001</v>
+        <v>2.1588</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1443</v>
+        <v>0.9075</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0037</v>
+        <v>1.2514</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.365</v>
+        <v>-0.8762</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3082</v>
+        <v>-1.0838</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0568</v>
+        <v>0.2075</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2249</v>
+        <v>-0.3912</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0351</v>
+        <v>-0.3222</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1898</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6458</v>
+        <v>2.5518</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2499</v>
+        <v>1.0887</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3959</v>
+        <v>1.4631</v>
       </c>
       <c r="G7" t="n">
         <v>1.052</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8979</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7196</v>
+        <v>0.5583</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1784</v>
+        <v>0.2456</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.271</v>
+        <v>2.5188</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2519</v>
+        <v>1.7254</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0192</v>
+        <v>0.7934</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1587</v>
+        <v>1.6058</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1367</v>
+        <v>-0.8368</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2953</v>
+        <v>2.4426</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9983</v>
+        <v>1.6634</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1715</v>
+        <v>-0.729</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8268</v>
+        <v>2.3923</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1603</v>
+        <v>-0.0576</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3082</v>
+        <v>-0.1078</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4685</v>
+        <v>0.0502</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4933</v>
+        <v>-0.3912</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2715</v>
+        <v>0.1496</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7648</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6627</v>
+        <v>1.0673</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3062</v>
+        <v>1.7781</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.7108</v>
       </c>
       <c r="G9" t="n">
         <v>3.9607</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4701</v>
+        <v>0.8746</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>0.3224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6194</v>
+        <v>0.5522</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3334</v>
+        <v>0.0608</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0588</v>
+        <v>-0.8662</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6975</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9208</v>
+        <v>1.315</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3383</v>
+        <v>0.5309</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5825</v>
+        <v>0.7842</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7886</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2933</v>
+        <v>-1.4837</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6879</v>
+        <v>-2.1455</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6054</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0642</v>
+        <v>-1.5524</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2641</v>
+        <v>-2.0442</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3284</v>
+        <v>0.4918</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4639</v>
+        <v>-0.9231</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2857</v>
+        <v>-2.2078</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.2847</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6004</v>
+        <v>-0.6293</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0216</v>
+        <v>0.1636</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5788</v>
+        <v>-0.7929</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1568</v>
+        <v>-0.1632</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.0626</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0672</v>
+        <v>-0.1006</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5856</v>
+        <v>-2.1925</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0458</v>
+        <v>-0.6879</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4602</v>
+        <v>-1.5046</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5524</v>
+        <v>-1.0642</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0442</v>
+        <v>0.2641</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4918</v>
+        <v>-1.3284</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9231</v>
+        <v>-0.4639</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2078</v>
+        <v>0.2857</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2847</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6293</v>
+        <v>-0.6004</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1636</v>
+        <v>-0.0216</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7929</v>
+        <v>-0.5788</v>
       </c>
       <c r="P12" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2652</v>
+        <v>-0.056</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.963</v>
+        <v>-0.224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3022</v>
+        <v>0.168</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.9958</v>
+        <v>25.3691</v>
       </c>
       <c r="E13" t="n">
-        <v>17.3617</v>
+        <v>17.7351</v>
       </c>
       <c r="F13" t="n">
-        <v>7.634200000000002</v>
+        <v>7.6341</v>
       </c>
       <c r="G13" t="n">
         <v>18.1187</v>
@@ -1438,7 +1438,7 @@
         <v>8.6496</v>
       </c>
       <c r="I13" t="n">
-        <v>9.468800000000002</v>
+        <v>9.4688</v>
       </c>
       <c r="J13" t="n">
         <v>20.3371</v>
@@ -1453,7 +1453,7 @@
         <v>-2.2185</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3457</v>
+        <v>-0.3457000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-1.873</v>
@@ -1468,16 +1468,16 @@
         <v>10.438</v>
       </c>
       <c r="S13" t="n">
-        <v>5.719799999999999</v>
+        <v>6.093100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.088299999999999</v>
+        <v>3.4617</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6314</v>
+        <v>2.6315</v>
       </c>
       <c r="V13" t="n">
-        <v>2.317300000000001</v>
+        <v>2.3173</v>
       </c>
       <c r="W13" t="n">
         <v>5.5339</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2014</v>
+        <v>1.6472</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9226</v>
+        <v>1.0406</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2787</v>
+        <v>0.6066</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1691</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9788</v>
+        <v>0.4246</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1019</v>
+        <v>0.016</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0807</v>
+        <v>0.4086</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5376</v>
+        <v>0.8521</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7199</v>
+        <v>1.7763</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1823</v>
+        <v>-0.9242</v>
       </c>
       <c r="G15" t="n">
         <v>0.4132</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7121</v>
+        <v>0.0266</v>
       </c>
       <c r="T15" t="n">
-        <v>1.274</v>
+        <v>0.3304</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5619</v>
+        <v>-0.3038</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2836</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4768</v>
+        <v>0.6284</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9361</v>
+        <v>4.0541</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4593</v>
+        <v>-3.4257</v>
       </c>
       <c r="G16" t="n">
         <v>2.9826</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8253</v>
+        <v>-1.6737</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1949</v>
+        <v>-1.0769</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6304</v>
+        <v>-0.5968</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4579</v>
+        <v>0.5923</v>
       </c>
       <c r="E17" t="n">
         <v>0.4255</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0324</v>
+        <v>0.1668</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8023</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.188</v>
+        <v>0.3224</v>
       </c>
       <c r="T17" t="n">
         <v>0.1968</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1256</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1775</v>
+        <v>0.5017</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5785</v>
+        <v>2.9324</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.756</v>
+        <v>-2.4307</v>
       </c>
       <c r="G18" t="n">
         <v>1.5632</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4211</v>
+        <v>-0.742</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7468</v>
+        <v>-0.393</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6743</v>
+        <v>-0.349</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-1.3658</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3222</v>
+        <v>-0.794</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5382</v>
+        <v>-0.5718</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3202</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4598</v>
+        <v>0.9544</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2072</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2526</v>
+        <v>0.219</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5361</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6964</v>
+        <v>-1.5956</v>
       </c>
       <c r="E20" t="n">
         <v>-1.0904</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.606</v>
+        <v>-0.5051</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6323</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8527</v>
+        <v>-0.7519</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4046</v>
+        <v>-0.3038</v>
       </c>
       <c r="V20" t="n">
         <v>0.7886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0743</v>
+        <v>-3.2436</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2636</v>
+        <v>-2.7918</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8108</v>
+        <v>-0.4518</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6805</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3216</v>
+        <v>0.5091</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1415</v>
+        <v>0.3304</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1801</v>
+        <v>0.1788</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1586</v>
+        <v>-3.8327</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7604</v>
+        <v>-2.5245</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3982</v>
+        <v>-1.3082</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0363</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7486</v>
+        <v>-0.4226</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3005</v>
+        <v>-0.2104</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8716</v>
+        <v>-3.9959</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1712</v>
+        <v>-3.4635</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7004</v>
+        <v>-0.5324</v>
       </c>
       <c r="G23" t="n">
         <v>-4.6102</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6531</v>
+        <v>-0.7773</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1123</v>
+        <v>-0.4046</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.3727</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3433</v>
+        <v>-6.7752</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.062</v>
+        <v>-3.4158</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2814</v>
+        <v>-3.3593</v>
       </c>
       <c r="G24" t="n">
         <v>-5.096</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.1431</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3339</v>
+        <v>-0.6877</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3774</v>
+        <v>-0.4553</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4873</v>
+        <v>-7.6224</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5471</v>
+        <v>-3.783</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.9402</v>
+        <v>-3.8394</v>
       </c>
       <c r="G25" t="n">
         <v>-3.7305</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5248</v>
+        <v>-1.6599</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.782</v>
+        <v>-1.0179</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7429</v>
+        <v>-0.642</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-24.9957</v>
+        <v>-24.2095</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.634299999999998</v>
+        <v>-7.6341</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.3617</v>
+        <v>-16.5752</v>
       </c>
       <c r="G26" t="n">
         <v>-18.1184</v>
@@ -2482,13 +2482,13 @@
         <v>11.5978</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.7197</v>
+        <v>-4.9334</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.6315</v>
+        <v>-2.6314</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.0884</v>
+        <v>-2.3018</v>
       </c>
       <c r="V26" t="n">
         <v>-2.3173</v>
